--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_182_R19.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_182_R19.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8669</v>
+        <v>1.3695</v>
       </c>
       <c r="E2" t="n">
-        <v>4.331</v>
+        <v>4.5984</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.4641</v>
+        <v>-3.2289</v>
       </c>
       <c r="G2" t="n">
         <v>3.0138</v>
@@ -610,13 +610,13 @@
         <v>0.6959</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.683</v>
+        <v>-1.1804</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8962</v>
+        <v>-0.6289</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.5515</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.696</v>
+        <v>0.7513</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1177</v>
+        <v>-0.1296</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8137</v>
+        <v>0.8809</v>
       </c>
       <c r="G3" t="n">
         <v>1.3671</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3311</v>
+        <v>-1.2757</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.6445</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6985</v>
+        <v>-0.6313</v>
       </c>
       <c r="V3" t="n">
         <v>1.3558</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1186</v>
+        <v>0.0252</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5874</v>
+        <v>1.662</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4688</v>
+        <v>-1.6368</v>
       </c>
       <c r="G4" t="n">
         <v>2.1563</v>
@@ -766,13 +766,13 @@
         <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3598</v>
+        <v>-0.4531</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8962</v>
+        <v>-0.8215</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5364</v>
+        <v>0.3684</v>
       </c>
       <c r="V4" t="n">
         <v>-1.214</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. BRYANT</t>
+          <t>I. WAINRIGHT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3656</v>
+        <v>-0.1008</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7116</v>
+        <v>1.4914</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.0772</v>
+        <v>-1.5921</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.581</v>
+        <v>-0.3106</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5052</v>
+        <v>-0.2377</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0321</v>
+        <v>2.5564</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9046</v>
+        <v>0.7933</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1275</v>
+        <v>1.7631</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.6131</v>
+        <v>-2.867</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9804</v>
+        <v>-0.8663</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6327</v>
+        <v>-2.0008</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-1.3416</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8566</v>
+        <v>-1.0651</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2886</v>
+        <v>-0.2765</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.6083</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. WAINRIGHT</t>
+          <t>E. BRYANT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5853</v>
+        <v>-0.5888</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8388</v>
+        <v>1.6565</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4241</v>
+        <v>-2.2452</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3106</v>
+        <v>-0.581</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2377</v>
+        <v>-0.5052</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5564</v>
+        <v>2.0321</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7933</v>
+        <v>0.9046</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7631</v>
+        <v>1.1275</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.867</v>
+        <v>-2.6131</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8663</v>
+        <v>-0.9804</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.0008</v>
+        <v>-1.6327</v>
       </c>
       <c r="P6" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.8262</v>
+        <v>-0.7912</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.7177</v>
+        <v>-0.9118000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1085</v>
+        <v>0.1206</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5361</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8927</v>
+        <v>-1.7919</v>
       </c>
       <c r="E7" t="n">
         <v>-1.2766</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6162</v>
+        <v>-0.5153</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1147</v>
@@ -1000,13 +1000,13 @@
         <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3141</v>
+        <v>-0.2133</v>
       </c>
       <c r="T7" t="n">
         <v>-0.224</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0901</v>
+        <v>0.0108</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5361</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4886</v>
+        <v>-2.7528</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1437</v>
+        <v>-1.2736</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3448</v>
+        <v>-1.4793</v>
       </c>
       <c r="G8" t="n">
         <v>-3.033</v>
@@ -1078,13 +1078,13 @@
         <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.007</v>
+        <v>-0.2713</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2592</v>
+        <v>-0.389</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2522</v>
+        <v>0.1177</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0722</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2855</v>
+        <v>-2.9435</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7208</v>
+        <v>-2.3788</v>
       </c>
       <c r="F9" t="n">
         <v>-0.5647</v>
@@ -1156,10 +1156,10 @@
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.8635</v>
+        <v>-1.5215</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3443</v>
+        <v>-1.0023</v>
       </c>
       <c r="U9" t="n">
         <v>-0.5192</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.512</v>
+        <v>-4.5495</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9519</v>
+        <v>-3.2246</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5601</v>
+        <v>-1.3249</v>
       </c>
       <c r="G10" t="n">
         <v>-4.69</v>
@@ -1234,13 +1234,13 @@
         <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.4456</v>
+        <v>-1.4831</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.643</v>
+        <v>-0.9157</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8026</v>
+        <v>-0.5673</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-12.4482</v>
+        <v>-10.5813</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7419000000000002</v>
+        <v>1.125099999999999</v>
       </c>
       <c r="F11" t="n">
         <v>-11.7063</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.773800000000001</v>
+        <v>-4.7738</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2492</v>
+        <v>1.249200000000001</v>
       </c>
       <c r="I11" t="n">
         <v>-6.023200000000001</v>
@@ -1291,7 +1291,7 @@
         <v>6.690200000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>3.194400000000001</v>
+        <v>3.194399999999999</v>
       </c>
       <c r="M11" t="n">
         <v>-14.6585</v>
@@ -1312,28 +1312,28 @@
         <v>11.5979</v>
       </c>
       <c r="S11" t="n">
-        <v>-10.3983</v>
+        <v>-8.5312</v>
       </c>
       <c r="T11" t="n">
-        <v>-8.469800000000001</v>
+        <v>-6.6028</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.9285</v>
+        <v>-1.9283</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.0748</v>
+        <v>-3.074800000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>3.642</v>
+        <v>3.641999999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.716800000000001</v>
+        <v>-6.7168</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. SLEVA</t>
+          <t>M. LO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.122</v>
+        <v>4.7535</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4021</v>
+        <v>3.2531</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7199</v>
+        <v>1.5004</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4805</v>
+        <v>3.5334</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3399</v>
+        <v>1.5426</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1406</v>
+        <v>1.9909</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4135</v>
+        <v>2.54</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1091</v>
+        <v>0.8101</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3044</v>
+        <v>1.7298</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9330000000000001</v>
+        <v>0.9935</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7692</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1638</v>
+        <v>0.261</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.6415</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1483</v>
+        <v>0.177</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4932</v>
+        <v>0.507</v>
       </c>
       <c r="V12" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. LO</t>
+          <t>D. SLEVA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.855</v>
+        <v>4.5493</v>
       </c>
       <c r="E13" t="n">
-        <v>3.489</v>
+        <v>2.9303</v>
       </c>
       <c r="F13" t="n">
-        <v>1.366</v>
+        <v>1.6191</v>
       </c>
       <c r="G13" t="n">
-        <v>3.5334</v>
+        <v>0.4805</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5426</v>
+        <v>0.3399</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9909</v>
+        <v>0.1406</v>
       </c>
       <c r="J13" t="n">
-        <v>2.54</v>
+        <v>1.4135</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8101</v>
+        <v>1.1091</v>
       </c>
       <c r="L13" t="n">
-        <v>1.7298</v>
+        <v>0.3044</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9935</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7324000000000001</v>
+        <v>-0.7692</v>
       </c>
       <c r="O13" t="n">
-        <v>0.261</v>
+        <v>-0.1638</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7855</v>
+        <v>2.0689</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4129</v>
+        <v>0.6765</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3725</v>
+        <v>1.3924</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. TUBELIS</t>
+          <t>I. BRAZDEIKIS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,58 +1501,58 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9101</v>
+        <v>2.6426</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5625</v>
+        <v>1.204</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3476</v>
+        <v>1.4386</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1886</v>
+        <v>1.3119</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4705</v>
+        <v>-1.3181</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6591</v>
+        <v>2.63</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8163</v>
+        <v>1.4014</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4186</v>
+        <v>-0.9173</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6022999999999999</v>
+        <v>2.3187</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0048</v>
+        <v>-0.0895</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9481000000000001</v>
+        <v>-0.4008</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0568</v>
+        <v>0.3113</v>
       </c>
       <c r="P14" t="n">
         <v>-0.6959</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7223</v>
+        <v>0.9544</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8338</v>
+        <v>0.1221</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8886</v>
+        <v>0.8323</v>
       </c>
       <c r="V14" t="n">
         <v>1.0722</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. BRAZDEIKIS</t>
+          <t>A. TUBELIS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5418</v>
+        <v>1.6983</v>
       </c>
       <c r="E15" t="n">
-        <v>1.204</v>
+        <v>0.8548</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3378</v>
+        <v>0.8435</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3119</v>
+        <v>-0.1886</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.3181</v>
+        <v>0.4705</v>
       </c>
       <c r="I15" t="n">
-        <v>2.63</v>
+        <v>-0.6591</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4014</v>
+        <v>0.8163</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.9173</v>
+        <v>1.4186</v>
       </c>
       <c r="L15" t="n">
-        <v>2.3187</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0895</v>
+        <v>-1.0048</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4008</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3113</v>
+        <v>-0.0568</v>
       </c>
       <c r="P15" t="n">
         <v>-0.6959</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8536</v>
+        <v>1.5105</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1221</v>
+        <v>0.1261</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7314000000000001</v>
+        <v>1.3845</v>
       </c>
       <c r="V15" t="n">
         <v>1.0722</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7735</v>
+        <v>0.8743</v>
       </c>
       <c r="E16" t="n">
         <v>2.0368</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2633</v>
+        <v>-1.1625</v>
       </c>
       <c r="G16" t="n">
         <v>0.2294</v>
@@ -1702,13 +1702,13 @@
         <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8457</v>
+        <v>0.9465</v>
       </c>
       <c r="T16" t="n">
         <v>0.3541</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4916</v>
+        <v>0.5924</v>
       </c>
       <c r="V16" t="n">
         <v>0.3943</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>A. BUTKEVICIUS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2689</v>
+        <v>0.556</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3813</v>
+        <v>2.4786</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6502</v>
+        <v>-1.9226</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4971</v>
+        <v>0.0523</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5774</v>
+        <v>-0.2857</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0804</v>
+        <v>0.338</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5034</v>
+        <v>2.5688</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.1659</v>
+        <v>1.2807</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6625</v>
+        <v>1.2882</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9937</v>
+        <v>-2.5165</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4116</v>
+        <v>-1.5664</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5821</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P17" t="n">
         <v>0.4639</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3021</v>
+        <v>0.3233</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3541</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.948</v>
+        <v>0.4136</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="18">
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BUTKEVICIUS</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1356</v>
+        <v>0.1345</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3606</v>
+        <v>-0.3813</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.225</v>
+        <v>0.5158</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0523</v>
+        <v>-1.4971</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2857</v>
+        <v>-1.5774</v>
       </c>
       <c r="I19" t="n">
-        <v>0.338</v>
+        <v>0.0804</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5688</v>
+        <v>-0.5034</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2807</v>
+        <v>-1.1659</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2882</v>
+        <v>0.6625</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.5165</v>
+        <v>-0.9937</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5664</v>
+        <v>-0.4116</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-0.5821</v>
       </c>
       <c r="P19" t="n">
         <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.09710000000000001</v>
+        <v>1.1677</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2082</v>
+        <v>0.3541</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1111</v>
+        <v>0.8136</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9683</v>
+        <v>0.0926</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.536</v>
+        <v>0.2897</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4323</v>
+        <v>-0.1971</v>
       </c>
       <c r="G20" t="n">
         <v>1.9083</v>
@@ -2014,13 +2014,13 @@
         <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4635</v>
+        <v>1.5244</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.507</v>
+        <v>0.3187</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9704</v>
+        <v>1.2057</v>
       </c>
       <c r="V20" t="n">
         <v>-0.7886</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0357</v>
+        <v>-0.581</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8578</v>
+        <v>-0.504</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1779</v>
+        <v>-0.077</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6182</v>
@@ -2092,13 +2092,13 @@
         <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3659</v>
+        <v>0.8206</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4323</v>
+        <v>-0.0784</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7982</v>
+        <v>0.899</v>
       </c>
       <c r="V21" t="n">
         <v>1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4068</v>
+        <v>-2.5241</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7562</v>
+        <v>-1.6382</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6506999999999999</v>
+        <v>-0.8859</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6902</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5153</v>
+        <v>0.398</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1494</v>
+        <v>-0.0314</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6647</v>
+        <v>0.4294</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>12.4482</v>
+        <v>12.4481</v>
       </c>
       <c r="E23" t="n">
-        <v>10.7758</v>
+        <v>10.7759</v>
       </c>
       <c r="F23" t="n">
-        <v>1.672299999999999</v>
+        <v>1.6723</v>
       </c>
       <c r="G23" t="n">
         <v>4.7738</v>
@@ -2224,10 +2224,10 @@
         <v>14.6586</v>
       </c>
       <c r="K23" t="n">
-        <v>5.441</v>
+        <v>5.440999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>9.217599999999999</v>
+        <v>9.217600000000001</v>
       </c>
       <c r="M23" t="n">
         <v>-9.884600000000001</v>
@@ -2251,10 +2251,10 @@
         <v>10.3983</v>
       </c>
       <c r="T23" t="n">
-        <v>1.9284</v>
+        <v>1.9285</v>
       </c>
       <c r="U23" t="n">
-        <v>8.4697</v>
+        <v>8.469900000000001</v>
       </c>
       <c r="V23" t="n">
         <v>3.0748</v>
